--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,12 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479065.7245489788</v>
+        <v>479066</v>
       </c>
       <c r="R3" t="n">
-        <v>6412381.058052048</v>
+        <v>6412381</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -872,19 +867,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -928,12 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479065.7245489788</v>
+        <v>479066</v>
       </c>
       <c r="R4" t="n">
-        <v>6412381.058052048</v>
+        <v>6412381</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -998,19 +978,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>74469005</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>74860976</v>
       </c>
       <c r="B4" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 410-2022 artfynd.xlsx
+++ b/artfynd/A 410-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64479763</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54677864</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16059276</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64479853</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1258,6 +1283,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55688998</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74469005</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1480,8 +1515,22 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74860976</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>